--- a/Apostas_Diarias/Apostas_20260401.xlsx
+++ b/Apostas_Diarias/Apostas_20260401.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_2B590F4F952642BCFBF38791481510344D07F712" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{786E291D-9A7E-40F2-A1DB-2F0CFD11D208}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2B590F4F95F64DB34FB38391481510344D07F712" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{138F19C5-1B03-4B82-A48B-625276B6E69C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
